--- a/data_processed/results_OLS_m2_floorarea_per_capitatenure.xlsx
+++ b/data_processed/results_OLS_m2_floorarea_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.5629" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.5636" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>139.9461610479979</v>
+        <v>139.4339114000706</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-8.210416874102247</v>
+        <v>-8.104872310765979</v>
       </c>
       <c r="D3" t="n">
-        <v>6.90033902090098e-168</v>
+        <v>2.006592964390031e-162</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-9.145008099159135</v>
+        <v>-13.67983125582412</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.663532194742791e-172</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3118946713448812</v>
+        <v>-9.123260920486217</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01831238451527559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.84650597016106</v>
+        <v>0.3159873777349005</v>
       </c>
       <c r="D6" t="n">
-        <v>7.838116842602695e-08</v>
+        <v>0.01089984787783668</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.00413424880521697</v>
+        <v>-1.816160004324251</v>
       </c>
       <c r="D7" t="n">
-        <v>1.521567906835602e-09</v>
+        <v>2.768453341963547e-12</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_middleschool</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.0008009099891358698</v>
+        <v>0.004540463965504988</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006453882924685394</v>
+        <v>3.690537036856495e-09</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-13.74435270192437</v>
+        <v>-0.0008771241458291686</v>
       </c>
       <c r="D9" t="n">
-        <v>7.264371374322219e-172</v>
+        <v>0.000564517557154868</v>
       </c>
     </row>
   </sheetData>
